--- a/Data Files/Backoffce/IndexacaoFG/Arquivos/Relatório de Recusas 26.05.2025 a 01.06.2025.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/Arquivos/Relatório de Recusas 26.05.2025 a 01.06.2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28922"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28926"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms.sharepoint.com/teams/BR0010-4356589/Shared Documents/BACK-OFFICE SME/Santander/2025/Relatório de Recusas/05. Maio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BAC14A1E-3E2D-4A96-9759-CE1A08AE8722}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DD112CE8-4C35-413A-8071-CD973DB5515F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="26.05" sheetId="8" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="89">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -242,23 +242,95 @@
     <t xml:space="preserve">SILVIO RODRIGUES                             </t>
   </si>
   <si>
-    <t>19/06/25</t>
-  </si>
-  <si>
-    <t>27/05/25</t>
-  </si>
-  <si>
     <t>MARCONE MOREIRA VALE CPF 49189123620</t>
   </si>
   <si>
     <t>Renovação de outro corretor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANDRESSA LUANA CARDOSO DOS SANTOS            </t>
+  </si>
+  <si>
+    <t>***FRUSTRADO***CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO - FOTO INCORRETA: Foto 45º - Frente e Lateral Esquerda baixa iluminação,Foto 45º - Frente e Lateral Direita baixa iluminção, Foto 45º - Traseira e Lateral Direita baixa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALEXANDER PERELLO DE FREITAS                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDMILSON DOMINGOS DOS SANTOS                 </t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 26.05.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDER ANTONIO DA SILVA                        </t>
+  </si>
+  <si>
+    <t>***FRUSTRADO***CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO - FOTO INCORRETA: Hodômetro (Foto Cortando Parte do Hodômetro).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JURANDIR DE ANDRADE                          </t>
+  </si>
+  <si>
+    <t>***FRUSTRADO***CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO - FOTO INCORRETA: HODOMETRO DESLIGADO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SHEILA MOREIRA SILVA BADARO                  </t>
+  </si>
+  <si>
+    <t>***FRUSTRADO***CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO - FOTO INCORRETA: Chassi (Foto do local incorreto.).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WALLAS JOSE DE ALMEIDA                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROMILTON SOARES DE OLIVEIRA                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVERALDO DA SILVA XAVIER                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUELLEN OLIVEIRA DA SILVA                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIEGO LOCATELI DE MELO FERREIRA              </t>
+  </si>
+  <si>
+    <t>Informamos que para prosseguirmos com o novo
+processo do Santander na proposta em referência, precisamos de re
+torno da pendência, com as informações abaixo:
+No aguardo do envio da cópia do endosso de cancelamento já emitido
+, com relação à classe de bônus, a correta é 7 devido apólice ante
+rior ter sofrido 2 sinistros.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRANCISCO ROBERTO GOMES PEREIRA              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISABEL CRISTINA CHAGAS BARBIN                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">APARECIDA MARTINS GOMES DELEFRATE            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">INGRID SANE DA SILVA BAIA                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVELINO DE OLIVEIRA JUNIOR ME                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DANIELE GOMES COSTA                          </t>
+  </si>
+  <si>
+    <t>Favor enviar cópia completa d
+a apólice anterior 2024/2025 ou CI atual .</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -285,11 +357,6 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -305,7 +372,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -420,21 +487,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thin">
         <color indexed="64"/>
@@ -452,7 +504,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -498,16 +550,13 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -975,7 +1024,7 @@
       <c r="H4" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="I4" s="23"/>
+      <c r="I4" s="22"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
@@ -1002,7 +1051,7 @@
       <c r="H5" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="I5" s="23">
+      <c r="I5" s="22">
         <v>45800</v>
       </c>
     </row>
@@ -1028,10 +1077,10 @@
       <c r="G6" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H6" s="24" t="s">
+      <c r="H6" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="I6" s="23">
+      <c r="I6" s="22">
         <v>45792</v>
       </c>
     </row>
@@ -1060,7 +1109,7 @@
       <c r="H7" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="I7" s="23">
+      <c r="I7" s="22">
         <v>45799</v>
       </c>
     </row>
@@ -1089,7 +1138,7 @@
       <c r="H8" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="I8" s="23">
+      <c r="I8" s="22">
         <v>45797</v>
       </c>
     </row>
@@ -1118,7 +1167,7 @@
       <c r="H9" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="I9" s="23">
+      <c r="I9" s="22">
         <v>45798</v>
       </c>
     </row>
@@ -1147,7 +1196,7 @@
       <c r="H10" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="I10" s="23">
+      <c r="I10" s="22">
         <v>45797</v>
       </c>
     </row>
@@ -1176,7 +1225,7 @@
       <c r="H11" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I11" s="23">
+      <c r="I11" s="22">
         <v>45796</v>
       </c>
     </row>
@@ -1205,7 +1254,7 @@
       <c r="H12" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="I12" s="23">
+      <c r="I12" s="22">
         <v>45798</v>
       </c>
     </row>
@@ -1231,10 +1280,10 @@
       <c r="G13" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H13" s="25" t="s">
+      <c r="H13" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="I13" s="23">
+      <c r="I13" s="22">
         <v>45810</v>
       </c>
     </row>
@@ -1263,7 +1312,7 @@
       <c r="H14" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="I14" s="23">
+      <c r="I14" s="22">
         <v>45797</v>
       </c>
     </row>
@@ -1292,7 +1341,7 @@
       <c r="H15" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="I15" s="23">
+      <c r="I15" s="22">
         <v>45796</v>
       </c>
     </row>
@@ -1318,10 +1367,10 @@
       <c r="G16" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H16" s="25" t="s">
+      <c r="H16" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="I16" s="23">
+      <c r="I16" s="22">
         <v>45793</v>
       </c>
     </row>
@@ -1347,10 +1396,10 @@
       <c r="G17" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H17" s="25" t="s">
+      <c r="H17" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="I17" s="23">
+      <c r="I17" s="22">
         <v>45800</v>
       </c>
     </row>
@@ -1379,7 +1428,7 @@
       <c r="H18" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="I18" s="23">
+      <c r="I18" s="22">
         <v>45797</v>
       </c>
     </row>
@@ -1408,7 +1457,7 @@
       <c r="H19" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="I19" s="23">
+      <c r="I19" s="22">
         <v>45799</v>
       </c>
     </row>
@@ -1437,7 +1486,7 @@
       <c r="H20" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="I20" s="23">
+      <c r="I20" s="22">
         <v>45798</v>
       </c>
     </row>
@@ -1466,7 +1515,7 @@
       <c r="H21" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="I21" s="23">
+      <c r="I21" s="22">
         <v>45793</v>
       </c>
     </row>
@@ -1495,7 +1544,7 @@
       <c r="H22" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="I22" s="23">
+      <c r="I22" s="22">
         <v>45793</v>
       </c>
     </row>
@@ -1524,7 +1573,7 @@
       <c r="H23" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="I23" s="23">
+      <c r="I23" s="22">
         <v>45793</v>
       </c>
     </row>
@@ -1553,7 +1602,7 @@
       <c r="H24" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="I24" s="23">
+      <c r="I24" s="22">
         <v>45793</v>
       </c>
     </row>
@@ -1582,7 +1631,7 @@
       <c r="H25" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="I25" s="23">
+      <c r="I25" s="22">
         <v>45800</v>
       </c>
     </row>
@@ -1611,7 +1660,7 @@
       <c r="H26" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="I26" s="23">
+      <c r="I26" s="22">
         <v>45793</v>
       </c>
     </row>
@@ -1640,7 +1689,7 @@
       <c r="H27" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="I27" s="23">
+      <c r="I27" s="22">
         <v>45793</v>
       </c>
     </row>
@@ -1669,7 +1718,7 @@
       <c r="H28" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="I28" s="23">
+      <c r="I28" s="22">
         <v>45793</v>
       </c>
     </row>
@@ -1698,7 +1747,7 @@
       <c r="H29" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="I29" s="23">
+      <c r="I29" s="22">
         <v>45793</v>
       </c>
     </row>
@@ -1992,13 +2041,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2FDCF22-758E-4370-8390-755171A8B113}">
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" customWidth="1"/>
     <col min="3" max="3" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.85546875" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" customWidth="1"/>
     <col min="6" max="6" width="40" customWidth="1"/>
     <col min="7" max="7" width="20.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="48.7109375" customWidth="1"/>
@@ -2038,255 +2087,525 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>64</v>
+      <c r="B2" s="7">
+        <v>45827</v>
+      </c>
+      <c r="C2" s="7">
+        <v>45804</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="21">
+      <c r="E2" s="8">
         <v>3449992359</v>
       </c>
-      <c r="F2" s="9" t="s">
-        <v>65</v>
+      <c r="F2" s="19" t="s">
+        <v>63</v>
       </c>
       <c r="G2" s="6" t="s">
         <v>14</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="19"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="9"/>
+      <c r="B3" s="7">
+        <v>45796</v>
+      </c>
+      <c r="C3" s="7">
+        <v>45804</v>
+      </c>
+      <c r="D3" s="8">
+        <v>132606478</v>
+      </c>
+      <c r="E3" s="14">
+        <v>3449988036</v>
+      </c>
+      <c r="F3" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="G3" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="22"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="11"/>
+      <c r="B4" s="7">
+        <v>45797</v>
+      </c>
+      <c r="C4" s="7">
+        <v>45804</v>
+      </c>
+      <c r="D4" s="8">
+        <v>132618949</v>
+      </c>
+      <c r="E4" s="14">
+        <v>3449988531</v>
+      </c>
+      <c r="F4" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="G4" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I4" s="11">
+        <v>45799</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="22"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="11"/>
+      <c r="B5" s="7">
+        <v>45797</v>
+      </c>
+      <c r="C5" s="7">
+        <v>45804</v>
+      </c>
+      <c r="D5" s="8">
+        <v>132618040</v>
+      </c>
+      <c r="E5" s="14">
+        <v>3449988454</v>
+      </c>
+      <c r="F5" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="G5" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="I5" s="11">
+        <v>45803</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="22"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="11"/>
+      <c r="B6" s="7">
+        <v>45794</v>
+      </c>
+      <c r="C6" s="7">
+        <v>45804</v>
+      </c>
+      <c r="D6" s="8">
+        <v>132604352</v>
+      </c>
+      <c r="E6" s="14">
+        <v>3449986518</v>
+      </c>
+      <c r="F6" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="G6" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="I6" s="11">
+        <v>45794</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="22"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="11"/>
+      <c r="B7" s="7">
+        <v>45796</v>
+      </c>
+      <c r="C7" s="7">
+        <v>45804</v>
+      </c>
+      <c r="D7" s="8">
+        <v>132608924</v>
+      </c>
+      <c r="E7" s="14">
+        <v>3449988135</v>
+      </c>
+      <c r="F7" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="G7" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="I7" s="11">
+        <v>45796</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="22"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="11"/>
+      <c r="B8" s="7">
+        <v>45798</v>
+      </c>
+      <c r="C8" s="7">
+        <v>45804</v>
+      </c>
+      <c r="D8" s="8">
+        <v>132636622</v>
+      </c>
+      <c r="E8" s="14">
+        <v>3449989378</v>
+      </c>
+      <c r="F8" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="G8" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="I8" s="11">
+        <v>45798</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="22"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="11"/>
+      <c r="B9" s="7">
+        <v>45799</v>
+      </c>
+      <c r="C9" s="7">
+        <v>45804</v>
+      </c>
+      <c r="D9" s="8">
+        <v>132654531</v>
+      </c>
+      <c r="E9" s="14">
+        <v>3449990412</v>
+      </c>
+      <c r="F9" s="23" t="s">
+        <v>76</v>
+      </c>
+      <c r="G9" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="I9" s="11">
+        <v>45799</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="22"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="11"/>
+      <c r="B10" s="7">
+        <v>45799</v>
+      </c>
+      <c r="C10" s="7">
+        <v>45804</v>
+      </c>
+      <c r="D10" s="8">
+        <v>132653627</v>
+      </c>
+      <c r="E10" s="14">
+        <v>3449990335</v>
+      </c>
+      <c r="F10" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="G10" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="I10" s="11">
+        <v>45799</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="22"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="11"/>
+      <c r="B11" s="7">
+        <v>45797</v>
+      </c>
+      <c r="C11" s="7">
+        <v>45804</v>
+      </c>
+      <c r="D11" s="8">
+        <v>132616192</v>
+      </c>
+      <c r="E11" s="14">
+        <v>3449988333</v>
+      </c>
+      <c r="F11" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="G11" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11" s="11">
+        <v>45797</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="20"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="11"/>
+      <c r="B12" s="7">
+        <v>45800</v>
+      </c>
+      <c r="C12" s="7">
+        <v>45804</v>
+      </c>
+      <c r="D12" s="8">
+        <v>132694053</v>
+      </c>
+      <c r="E12" s="14">
+        <v>3449991336</v>
+      </c>
+      <c r="F12" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="G12" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="I12" s="11">
+        <v>45800</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="11"/>
+      <c r="B13" s="7">
+        <v>45790</v>
+      </c>
+      <c r="C13" s="7">
+        <v>45804</v>
+      </c>
+      <c r="D13" s="8">
+        <v>132538834</v>
+      </c>
+      <c r="E13" s="14">
+        <v>3449984087</v>
+      </c>
+      <c r="F13" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="G13" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="H13" s="24" t="s">
+        <v>81</v>
+      </c>
+      <c r="I13" s="11">
+        <v>45800</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="11"/>
+      <c r="B14" s="7">
+        <v>45796</v>
+      </c>
+      <c r="C14" s="7">
+        <v>45804</v>
+      </c>
+      <c r="D14" s="8">
+        <v>132604477</v>
+      </c>
+      <c r="E14" s="14">
+        <v>3449987959</v>
+      </c>
+      <c r="F14" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="G14" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="I14" s="11">
+        <v>45796</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="11"/>
+      <c r="B15" s="7">
+        <v>45793</v>
+      </c>
+      <c r="C15" s="7">
+        <v>45804</v>
+      </c>
+      <c r="D15" s="8">
+        <v>132604818</v>
+      </c>
+      <c r="E15" s="14">
+        <v>3449986540</v>
+      </c>
+      <c r="F15" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="G15" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="I15" s="11">
+        <v>45793</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="11"/>
+      <c r="B16" s="7">
+        <v>45798</v>
+      </c>
+      <c r="C16" s="7">
+        <v>45804</v>
+      </c>
+      <c r="D16" s="8">
+        <v>132654029</v>
+      </c>
+      <c r="E16" s="14">
+        <v>3449989587</v>
+      </c>
+      <c r="F16" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="G16" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="I16" s="11">
+        <v>45798</v>
+      </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="11"/>
+      <c r="B17" s="7">
+        <v>45796</v>
+      </c>
+      <c r="C17" s="7">
+        <v>45804</v>
+      </c>
+      <c r="D17" s="8">
+        <v>132606608</v>
+      </c>
+      <c r="E17" s="14">
+        <v>3449988047</v>
+      </c>
+      <c r="F17" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="G17" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="I17" s="11">
+        <v>45796</v>
+      </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="11"/>
+      <c r="B18" s="7">
+        <v>45799</v>
+      </c>
+      <c r="C18" s="7">
+        <v>45804</v>
+      </c>
+      <c r="D18" s="8">
+        <v>132676092</v>
+      </c>
+      <c r="E18" s="14">
+        <v>3449990313</v>
+      </c>
+      <c r="F18" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="G18" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="I18" s="11">
+        <v>45799</v>
+      </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="11"/>
+      <c r="B19" s="7">
+        <v>45791</v>
+      </c>
+      <c r="C19" s="7">
+        <v>45804</v>
+      </c>
+      <c r="D19" s="8">
+        <v>132565590</v>
+      </c>
+      <c r="E19" s="14">
+        <v>3449983560</v>
+      </c>
+      <c r="F19" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="G19" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="H19" s="24" t="s">
+        <v>88</v>
+      </c>
+      <c r="I19" s="11">
+        <v>45796</v>
+      </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="6"/>
       <c r="B20" s="8"/>
       <c r="C20" s="7"/>
       <c r="D20" s="8"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="13"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="15"/>
       <c r="G20" s="6"/>
       <c r="H20" s="9"/>
     </row>
@@ -2296,7 +2615,7 @@
       <c r="C21" s="7"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
-      <c r="F21" s="15"/>
+      <c r="F21" s="9"/>
       <c r="G21" s="6"/>
       <c r="H21" s="9"/>
     </row>
@@ -2640,30 +2959,20 @@
       <c r="G55" s="6"/>
       <c r="H55" s="9"/>
     </row>
-    <row r="56" spans="1:8">
-      <c r="A56" s="6"/>
-      <c r="B56" s="8"/>
-      <c r="C56" s="7"/>
-      <c r="D56" s="8"/>
-      <c r="E56" s="8"/>
-      <c r="F56" s="9"/>
-      <c r="G56" s="6"/>
-      <c r="H56" s="9"/>
-    </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="2">
+    <cfRule type="notContainsBlanks" priority="3">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  <conditionalFormatting sqref="F3:F19 D3:D19">
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
   </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A19" xr:uid="{7F37C4BE-D63E-47ED-BF24-8984F0F2FDF4}">
       <formula1>$J$2</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G42" xr:uid="{A652E7D6-65BA-4CC5-BE0C-6E061C2F44AC}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G41" xr:uid="{A652E7D6-65BA-4CC5-BE0C-6E061C2F44AC}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6073,110 +6382,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-469103</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-469103</Url>
-      <Description>QAFFA7D2F2TC-2102087286-469103</Description>
-    </_dlc_DocIdUrl>
-    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </DossierOwner>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ccca9d190a3c43e89f73773ee806c8b5>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ia4b831ccad64069ad2e0cbd870e9b8a>
-    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </alteradopor>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="43" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="32fbec5585ae01a22f32af5838af0c4d">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7b2552458edfdc024ce707f91c2c891f" ns1:_="" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="43" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="abf1b9912853fe4a934dbc2373304754">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d8d96f03b10d24171ef462918d18284e" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
     <xsd:import namespace="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea"/>
     <xsd:import namespace="ea6c6725-5210-4d6a-93cc-4cf85111ac5e"/>
@@ -6224,12 +6431,12 @@
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="http://schemas.microsoft.com/sharepoint/v3" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="_ip_UnifiedCompliancePolicyProperties" ma:index="23" nillable="true" ma:displayName="Propriedades da Política de Conformidade Unificada" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyProperties">
+    <xsd:element name="_ip_UnifiedCompliancePolicyProperties" ma:index="23" nillable="true" ma:displayName="Unified Compliance Policy Properties" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyProperties">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="_ip_UnifiedCompliancePolicyUIAction" ma:index="24" nillable="true" ma:displayName="Ação de IU da Política de Conformidade Unificada" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyUIAction">
+    <xsd:element name="_ip_UnifiedCompliancePolicyUIAction" ma:index="24" nillable="true" ma:displayName="Unified Compliance Policy UI Action" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyUIAction">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
@@ -6238,12 +6445,12 @@
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="_dlc_DocId" ma:index="8" nillable="true" ma:displayName="Valor do ID do Documento" ma:description="O valor do ID do documento atribuído a este item." ma:indexed="true" ma:internalName="_dlc_DocId" ma:readOnly="true">
+    <xsd:element name="_dlc_DocId" ma:index="8" nillable="true" ma:displayName="Document ID Value" ma:description="The value of the document ID assigned to this item." ma:indexed="true" ma:internalName="_dlc_DocId" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="_dlc_DocIdUrl" ma:index="9" nillable="true" ma:displayName="ID do Documento" ma:description="Ligação permanente a este documento." ma:hidden="true" ma:internalName="_dlc_DocIdUrl" ma:readOnly="true">
+    <xsd:element name="_dlc_DocIdUrl" ma:index="9" nillable="true" ma:displayName="Document ID" ma:description="Permanent link to this document." ma:hidden="true" ma:internalName="_dlc_DocIdUrl" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:URL">
@@ -6326,7 +6533,7 @@
         <xsd:restriction base="dms:DateTime"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Partilhado Com" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -6345,7 +6552,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Detalhes de Partilhado Com" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
@@ -6378,7 +6585,7 @@
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="26" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de Imagem" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="10820af1-e82f-496e-bbcb-d9502914b7b2" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="26" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="10820af1-e82f-496e-bbcb-d9502914b7b2" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
@@ -6456,8 +6663,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de Conteúdo"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -6546,18 +6753,120 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-469103</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-469103</Url>
+      <Description>QAFFA7D2F2TC-2102087286-469103</Description>
+    </_dlc_DocIdUrl>
+    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </DossierOwner>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ccca9d190a3c43e89f73773ee806c8b5>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ia4b831ccad64069ad2e0cbd870e9b8a>
+    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </alteradopor>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{422E86E5-4CC6-443E-A0AA-A74CA8044393}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
-</file>
-
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D80D24DD-097F-472C-9518-575517F439B2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/Arquivos/Relatório de Recusas 26.05.2025 a 01.06.2025.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/Arquivos/Relatório de Recusas 26.05.2025 a 01.06.2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms.sharepoint.com/teams/BR0010-4356589/Shared Documents/BACK-OFFICE SME/Santander/2025/Relatório de Recusas/05. Maio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DD112CE8-4C35-413A-8071-CD973DB5515F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E2DE80A4-4FF4-460E-95DE-43B1A2B40EEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="26.05" sheetId="8" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="123">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -324,6 +324,111 @@
   <si>
     <t>Favor enviar cópia completa d
 a apólice anterior 2024/2025 ou CI atual .</t>
+  </si>
+  <si>
+    <t>28/05/2025</t>
+  </si>
+  <si>
+    <t>LEANDRO DE PAULA SARTO CPF 04808172607</t>
+  </si>
+  <si>
+    <t>CI INCORRETA</t>
+  </si>
+  <si>
+    <t>21/05/2025</t>
+  </si>
+  <si>
+    <t>ERIBALDO GOIS CPF 35967129715</t>
+  </si>
+  <si>
+    <t>Apólice ativa com outro Corretor</t>
+  </si>
+  <si>
+    <t>27/05/2025</t>
+  </si>
+  <si>
+    <t>IVORI PALMERA CPF 63617781934</t>
+  </si>
+  <si>
+    <t>Redução de bonus por sinistro</t>
+  </si>
+  <si>
+    <t>MARIA DELPHINO CPF 00277349869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FERNANDO ANTONIO DE BARCELOS                 </t>
+  </si>
+  <si>
+    <t>Recusa a pedido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MASSAMITSU ALBERTO IKO                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">KATIA GARBELINI BOMFIM                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELSON FRANCISCO DO NASCIMENTO                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUELI TRANSPORTES LTDA ME                    </t>
+  </si>
+  <si>
+    <t>***FRUSTRADO***CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO - FOTO INCORRETA:Documento do veículo (Foto cortando as observações, Foto com dificuldade de leitura do documento). Foto 45º - Frente e Lateral Direita</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA JOSE DE SOUZA BRITO                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRISTIAN KLOCK DEUDEGANT                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PATRICIA FERREIRA TOLARI                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALISSON DA SILVA IGNACIO                     </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, identificamos que não há po
+ssibilidade de efetuar a transferência de bônus para o(a) senhor(a
+) ALISSON DA SILVA IGNACIO, pois este não consta como condutor na
+apólice anterior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JARDANIELE DE SOUSA ALVES                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MANOEL BATISTA DE ALMEIDA JUNIOR             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">IVAN DAGOBERTO RIBEIRO ALVES                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MANOEL LAZARO PEREIRA BORGES                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLAUDIA TIEKO FURUCHO                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DENYLSON SOUZA REIS LTDA ME                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">WELINGTON OLIVEIRA DOS SANTOS                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">WILSON DA SILVA DE SOUZA                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRISCILA MADUREIRA NASCIMENTO                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">STELA GUARDA MOYA CHAVES                     </t>
+  </si>
+  <si>
+    <t>***FRUSTRADO***CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO - FOTO INCORRETA: TODOS OS PASSOS PENDENTES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JACKELLINNE DE SOUSA PEREIRA SCHNEIDER       </t>
   </si>
 </sst>
 </file>
@@ -504,7 +609,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -539,9 +644,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -915,7 +1017,7 @@
     <col min="6" max="6" width="27.42578125" customWidth="1"/>
     <col min="7" max="7" width="20.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="42.5703125" customWidth="1"/>
-    <col min="9" max="9" width="18.7109375" style="17" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.7109375" style="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -1024,7 +1126,7 @@
       <c r="H4" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="I4" s="22"/>
+      <c r="I4" s="21"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
@@ -1051,7 +1153,7 @@
       <c r="H5" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="I5" s="22">
+      <c r="I5" s="21">
         <v>45800</v>
       </c>
     </row>
@@ -1077,10 +1179,10 @@
       <c r="G6" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H6" s="19" t="s">
+      <c r="H6" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="I6" s="22">
+      <c r="I6" s="21">
         <v>45792</v>
       </c>
     </row>
@@ -1103,13 +1205,13 @@
       <c r="F7" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="G7" s="18" t="s">
+      <c r="G7" s="17" t="s">
         <v>22</v>
       </c>
       <c r="H7" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="I7" s="22">
+      <c r="I7" s="21">
         <v>45799</v>
       </c>
     </row>
@@ -1132,13 +1234,13 @@
       <c r="F8" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G8" s="18" t="s">
+      <c r="G8" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="H8" s="20" t="s">
+      <c r="H8" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="I8" s="22">
+      <c r="I8" s="21">
         <v>45797</v>
       </c>
     </row>
@@ -1167,7 +1269,7 @@
       <c r="H9" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="I9" s="22">
+      <c r="I9" s="21">
         <v>45798</v>
       </c>
     </row>
@@ -1196,7 +1298,7 @@
       <c r="H10" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="I10" s="22">
+      <c r="I10" s="21">
         <v>45797</v>
       </c>
     </row>
@@ -1225,7 +1327,7 @@
       <c r="H11" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I11" s="22">
+      <c r="I11" s="21">
         <v>45796</v>
       </c>
     </row>
@@ -1254,7 +1356,7 @@
       <c r="H12" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="I12" s="22">
+      <c r="I12" s="21">
         <v>45798</v>
       </c>
     </row>
@@ -1283,7 +1385,7 @@
       <c r="H13" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="I13" s="22">
+      <c r="I13" s="21">
         <v>45810</v>
       </c>
     </row>
@@ -1312,7 +1414,7 @@
       <c r="H14" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="I14" s="22">
+      <c r="I14" s="21">
         <v>45797</v>
       </c>
     </row>
@@ -1341,7 +1443,7 @@
       <c r="H15" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="I15" s="22">
+      <c r="I15" s="21">
         <v>45796</v>
       </c>
     </row>
@@ -1370,7 +1472,7 @@
       <c r="H16" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="I16" s="22">
+      <c r="I16" s="21">
         <v>45793</v>
       </c>
     </row>
@@ -1399,7 +1501,7 @@
       <c r="H17" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="I17" s="22">
+      <c r="I17" s="21">
         <v>45800</v>
       </c>
     </row>
@@ -1428,7 +1530,7 @@
       <c r="H18" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="I18" s="22">
+      <c r="I18" s="21">
         <v>45797</v>
       </c>
     </row>
@@ -1457,7 +1559,7 @@
       <c r="H19" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="I19" s="22">
+      <c r="I19" s="21">
         <v>45799</v>
       </c>
     </row>
@@ -1486,7 +1588,7 @@
       <c r="H20" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="I20" s="22">
+      <c r="I20" s="21">
         <v>45798</v>
       </c>
     </row>
@@ -1515,7 +1617,7 @@
       <c r="H21" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="I21" s="22">
+      <c r="I21" s="21">
         <v>45793</v>
       </c>
     </row>
@@ -1544,7 +1646,7 @@
       <c r="H22" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="I22" s="22">
+      <c r="I22" s="21">
         <v>45793</v>
       </c>
     </row>
@@ -1573,7 +1675,7 @@
       <c r="H23" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="I23" s="22">
+      <c r="I23" s="21">
         <v>45793</v>
       </c>
     </row>
@@ -1602,7 +1704,7 @@
       <c r="H24" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="I24" s="22">
+      <c r="I24" s="21">
         <v>45793</v>
       </c>
     </row>
@@ -1631,7 +1733,7 @@
       <c r="H25" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="I25" s="22">
+      <c r="I25" s="21">
         <v>45800</v>
       </c>
     </row>
@@ -1660,7 +1762,7 @@
       <c r="H26" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="I26" s="22">
+      <c r="I26" s="21">
         <v>45793</v>
       </c>
     </row>
@@ -1689,7 +1791,7 @@
       <c r="H27" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="I27" s="22">
+      <c r="I27" s="21">
         <v>45793</v>
       </c>
     </row>
@@ -1718,7 +1820,7 @@
       <c r="H28" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="I28" s="22">
+      <c r="I28" s="21">
         <v>45793</v>
       </c>
     </row>
@@ -1747,7 +1849,7 @@
       <c r="H29" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="I29" s="22">
+      <c r="I29" s="21">
         <v>45793</v>
       </c>
     </row>
@@ -2099,7 +2201,7 @@
       <c r="E2" s="8">
         <v>3449992359</v>
       </c>
-      <c r="F2" s="19" t="s">
+      <c r="F2" s="18" t="s">
         <v>63</v>
       </c>
       <c r="G2" s="6" t="s">
@@ -2125,10 +2227,10 @@
       <c r="E3" s="14">
         <v>3449988036</v>
       </c>
-      <c r="F3" s="23" t="s">
+      <c r="F3" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="G3" s="21" t="s">
+      <c r="G3" s="20" t="s">
         <v>34</v>
       </c>
       <c r="H3" s="9" t="s">
@@ -2151,10 +2253,10 @@
       <c r="E4" s="14">
         <v>3449988531</v>
       </c>
-      <c r="F4" s="23" t="s">
+      <c r="F4" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="G4" s="21" t="s">
+      <c r="G4" s="20" t="s">
         <v>22</v>
       </c>
       <c r="H4" s="9" t="s">
@@ -2180,10 +2282,10 @@
       <c r="E5" s="14">
         <v>3449988454</v>
       </c>
-      <c r="F5" s="23" t="s">
+      <c r="F5" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="G5" s="21" t="s">
+      <c r="G5" s="20" t="s">
         <v>22</v>
       </c>
       <c r="H5" s="9" t="s">
@@ -2209,10 +2311,10 @@
       <c r="E6" s="14">
         <v>3449986518</v>
       </c>
-      <c r="F6" s="23" t="s">
+      <c r="F6" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="G6" s="21" t="s">
+      <c r="G6" s="20" t="s">
         <v>34</v>
       </c>
       <c r="H6" s="9" t="s">
@@ -2238,10 +2340,10 @@
       <c r="E7" s="14">
         <v>3449988135</v>
       </c>
-      <c r="F7" s="23" t="s">
+      <c r="F7" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="G7" s="21" t="s">
+      <c r="G7" s="20" t="s">
         <v>34</v>
       </c>
       <c r="H7" s="10" t="s">
@@ -2267,10 +2369,10 @@
       <c r="E8" s="14">
         <v>3449989378</v>
       </c>
-      <c r="F8" s="23" t="s">
+      <c r="F8" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="G8" s="21" t="s">
+      <c r="G8" s="20" t="s">
         <v>34</v>
       </c>
       <c r="H8" s="10" t="s">
@@ -2296,10 +2398,10 @@
       <c r="E9" s="14">
         <v>3449990412</v>
       </c>
-      <c r="F9" s="23" t="s">
+      <c r="F9" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="G9" s="21" t="s">
+      <c r="G9" s="20" t="s">
         <v>34</v>
       </c>
       <c r="H9" s="9" t="s">
@@ -2325,10 +2427,10 @@
       <c r="E10" s="14">
         <v>3449990335</v>
       </c>
-      <c r="F10" s="23" t="s">
+      <c r="F10" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="G10" s="21" t="s">
+      <c r="G10" s="20" t="s">
         <v>30</v>
       </c>
       <c r="H10" s="9" t="s">
@@ -2354,10 +2456,10 @@
       <c r="E11" s="14">
         <v>3449988333</v>
       </c>
-      <c r="F11" s="23" t="s">
+      <c r="F11" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="G11" s="21" t="s">
+      <c r="G11" s="20" t="s">
         <v>30</v>
       </c>
       <c r="H11" s="9" t="s">
@@ -2383,10 +2485,10 @@
       <c r="E12" s="14">
         <v>3449991336</v>
       </c>
-      <c r="F12" s="23" t="s">
+      <c r="F12" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="G12" s="21" t="s">
+      <c r="G12" s="20" t="s">
         <v>30</v>
       </c>
       <c r="H12" s="9" t="s">
@@ -2412,13 +2514,13 @@
       <c r="E13" s="14">
         <v>3449984087</v>
       </c>
-      <c r="F13" s="23" t="s">
+      <c r="F13" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="G13" s="21" t="s">
+      <c r="G13" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="H13" s="24" t="s">
+      <c r="H13" s="9" t="s">
         <v>81</v>
       </c>
       <c r="I13" s="11">
@@ -2441,10 +2543,10 @@
       <c r="E14" s="14">
         <v>3449987959</v>
       </c>
-      <c r="F14" s="23" t="s">
+      <c r="F14" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="G14" s="21" t="s">
+      <c r="G14" s="20" t="s">
         <v>53</v>
       </c>
       <c r="H14" s="9" t="s">
@@ -2470,10 +2572,10 @@
       <c r="E15" s="14">
         <v>3449986540</v>
       </c>
-      <c r="F15" s="23" t="s">
+      <c r="F15" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="G15" s="21" t="s">
+      <c r="G15" s="20" t="s">
         <v>53</v>
       </c>
       <c r="H15" s="9" t="s">
@@ -2499,10 +2601,10 @@
       <c r="E16" s="14">
         <v>3449989587</v>
       </c>
-      <c r="F16" s="23" t="s">
+      <c r="F16" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="G16" s="21" t="s">
+      <c r="G16" s="20" t="s">
         <v>34</v>
       </c>
       <c r="H16" s="9" t="s">
@@ -2528,10 +2630,10 @@
       <c r="E17" s="14">
         <v>3449988047</v>
       </c>
-      <c r="F17" s="23" t="s">
+      <c r="F17" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="G17" s="21" t="s">
+      <c r="G17" s="20" t="s">
         <v>53</v>
       </c>
       <c r="H17" s="9" t="s">
@@ -2557,10 +2659,10 @@
       <c r="E18" s="14">
         <v>3449990313</v>
       </c>
-      <c r="F18" s="23" t="s">
+      <c r="F18" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="G18" s="21" t="s">
+      <c r="G18" s="20" t="s">
         <v>30</v>
       </c>
       <c r="H18" s="9" t="s">
@@ -2586,13 +2688,13 @@
       <c r="E19" s="14">
         <v>3449983560</v>
       </c>
-      <c r="F19" s="23" t="s">
+      <c r="F19" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="G19" s="21" t="s">
+      <c r="G19" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="H19" s="24" t="s">
+      <c r="H19" s="9" t="s">
         <v>88</v>
       </c>
       <c r="I19" s="11">
@@ -2982,17 +3084,17 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFA17127-7620-4DD9-9061-6C654E2EC5C2}">
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I53"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="20.42578125" customWidth="1"/>
-    <col min="3" max="3" width="21.5703125" customWidth="1"/>
-    <col min="4" max="4" width="27.7109375" customWidth="1"/>
-    <col min="5" max="5" width="28" customWidth="1"/>
-    <col min="6" max="6" width="52.85546875" customWidth="1"/>
-    <col min="7" max="7" width="23.140625" customWidth="1"/>
-    <col min="8" max="8" width="32.140625" customWidth="1"/>
+    <col min="1" max="1" width="10.28515625" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" customWidth="1"/>
+    <col min="3" max="3" width="15.140625" customWidth="1"/>
+    <col min="4" max="4" width="18.140625" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" customWidth="1"/>
+    <col min="6" max="6" width="35.5703125" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="37" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="22.7109375" style="16" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3029,301 +3131,687 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="9"/>
-      <c r="I2"/>
+      <c r="B2" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="8">
+        <v>3449992106</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="9"/>
-      <c r="I3"/>
+      <c r="B3" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="8">
+        <v>3449989521</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="11"/>
+      <c r="B4" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="8">
+        <v>3449993151</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="I4" s="21"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="11"/>
+      <c r="B5" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="8">
+        <v>3449990676</v>
+      </c>
+      <c r="F5" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" s="21"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="11"/>
+      <c r="B6" s="7">
+        <v>45806</v>
+      </c>
+      <c r="C6" s="7">
+        <v>45805</v>
+      </c>
+      <c r="D6" s="8">
+        <v>132646946</v>
+      </c>
+      <c r="E6" s="14">
+        <v>3449990137</v>
+      </c>
+      <c r="F6" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="G6" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="I6" s="21">
+        <v>45800</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="11"/>
+      <c r="B7" s="7">
+        <v>45792</v>
+      </c>
+      <c r="C7" s="7">
+        <v>45805</v>
+      </c>
+      <c r="D7" s="8">
+        <v>132554020</v>
+      </c>
+      <c r="E7" s="14">
+        <v>3449985430</v>
+      </c>
+      <c r="F7" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="G7" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="I7" s="21">
+        <v>45796</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="11"/>
+      <c r="B8" s="7">
+        <v>45800</v>
+      </c>
+      <c r="C8" s="7">
+        <v>45805</v>
+      </c>
+      <c r="D8" s="8">
+        <v>132681777</v>
+      </c>
+      <c r="E8" s="14">
+        <v>3449991700</v>
+      </c>
+      <c r="F8" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="G8" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="I8" s="21">
+        <v>45798</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="11"/>
+      <c r="B9" s="7">
+        <v>45832</v>
+      </c>
+      <c r="C9" s="7">
+        <v>45805</v>
+      </c>
+      <c r="D9" s="8">
+        <v>132695615</v>
+      </c>
+      <c r="E9" s="14">
+        <v>3449992260</v>
+      </c>
+      <c r="F9" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="G9" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="I9" s="21">
+        <v>45803</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="11"/>
+      <c r="B10" s="7">
+        <v>45798</v>
+      </c>
+      <c r="C10" s="7">
+        <v>45805</v>
+      </c>
+      <c r="D10" s="8">
+        <v>132636274</v>
+      </c>
+      <c r="E10" s="14">
+        <v>3449989345</v>
+      </c>
+      <c r="F10" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="G10" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="I10" s="21">
+        <v>45798</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="11"/>
+      <c r="B11" s="7">
+        <v>45800</v>
+      </c>
+      <c r="C11" s="7">
+        <v>45805</v>
+      </c>
+      <c r="D11" s="8">
+        <v>132670726</v>
+      </c>
+      <c r="E11" s="14">
+        <v>3449991259</v>
+      </c>
+      <c r="F11" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="G11" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11" s="21">
+        <v>45800</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="11"/>
+      <c r="B12" s="7">
+        <v>45800</v>
+      </c>
+      <c r="C12" s="7">
+        <v>45805</v>
+      </c>
+      <c r="D12" s="8">
+        <v>132684046</v>
+      </c>
+      <c r="E12" s="14">
+        <v>3449991810</v>
+      </c>
+      <c r="F12" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="G12" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="I12" s="21">
+        <v>45800</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="11"/>
+      <c r="B13" s="7">
+        <v>45798</v>
+      </c>
+      <c r="C13" s="7">
+        <v>45805</v>
+      </c>
+      <c r="D13" s="8">
+        <v>132651893</v>
+      </c>
+      <c r="E13" s="14">
+        <v>3449990071</v>
+      </c>
+      <c r="F13" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G13" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="I13" s="21">
+        <v>45798</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="11"/>
+      <c r="B14" s="7">
+        <v>45800</v>
+      </c>
+      <c r="C14" s="7">
+        <v>45805</v>
+      </c>
+      <c r="D14" s="8">
+        <v>132694793</v>
+      </c>
+      <c r="E14" s="14">
+        <v>3449991578</v>
+      </c>
+      <c r="F14" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="G14" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="H14" s="23" t="s">
+        <v>110</v>
+      </c>
+      <c r="I14" s="21">
+        <v>45805</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="11"/>
+      <c r="B15" s="7">
+        <v>45797</v>
+      </c>
+      <c r="C15" s="7">
+        <v>45805</v>
+      </c>
+      <c r="D15" s="8">
+        <v>132613922</v>
+      </c>
+      <c r="E15" s="14">
+        <v>3449988245</v>
+      </c>
+      <c r="F15" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="G15" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="I15" s="21">
+        <v>45797</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="11"/>
+      <c r="B16" s="7">
+        <v>45797</v>
+      </c>
+      <c r="C16" s="7">
+        <v>45805</v>
+      </c>
+      <c r="D16" s="8">
+        <v>132618130</v>
+      </c>
+      <c r="E16" s="14">
+        <v>3449988465</v>
+      </c>
+      <c r="F16" s="22" t="s">
+        <v>112</v>
+      </c>
+      <c r="G16" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="I16" s="21">
+        <v>45797</v>
+      </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="11"/>
+      <c r="B17" s="7">
+        <v>45792</v>
+      </c>
+      <c r="C17" s="7">
+        <v>45805</v>
+      </c>
+      <c r="D17" s="8">
+        <v>132622883</v>
+      </c>
+      <c r="E17" s="14">
+        <v>3449986012</v>
+      </c>
+      <c r="F17" s="22" t="s">
+        <v>113</v>
+      </c>
+      <c r="G17" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="I17" s="21">
+        <v>45792</v>
+      </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="11"/>
+      <c r="B18" s="7">
+        <v>45796</v>
+      </c>
+      <c r="C18" s="7">
+        <v>45805</v>
+      </c>
+      <c r="D18" s="8">
+        <v>132626529</v>
+      </c>
+      <c r="E18" s="14">
+        <v>3449987728</v>
+      </c>
+      <c r="F18" s="22" t="s">
+        <v>114</v>
+      </c>
+      <c r="G18" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="I18" s="21">
+        <v>45796</v>
+      </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="11"/>
+      <c r="B19" s="7">
+        <v>45796</v>
+      </c>
+      <c r="C19" s="7">
+        <v>45805</v>
+      </c>
+      <c r="D19" s="8">
+        <v>132627611</v>
+      </c>
+      <c r="E19" s="14">
+        <v>3449987574</v>
+      </c>
+      <c r="F19" s="22" t="s">
+        <v>115</v>
+      </c>
+      <c r="G19" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="I19" s="21">
+        <v>45796</v>
+      </c>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="6"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="9"/>
-      <c r="I20"/>
+      <c r="A20" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="7">
+        <v>45797</v>
+      </c>
+      <c r="C20" s="7">
+        <v>45805</v>
+      </c>
+      <c r="D20" s="8">
+        <v>132628178</v>
+      </c>
+      <c r="E20" s="14">
+        <v>3449988982</v>
+      </c>
+      <c r="F20" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="G20" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="I20" s="21">
+        <v>45797</v>
+      </c>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="6"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="9"/>
-      <c r="I21"/>
+      <c r="A21" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="7">
+        <v>45797</v>
+      </c>
+      <c r="C21" s="7">
+        <v>45805</v>
+      </c>
+      <c r="D21" s="8">
+        <v>132628958</v>
+      </c>
+      <c r="E21" s="14">
+        <v>3449989048</v>
+      </c>
+      <c r="F21" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="G21" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="I21" s="21">
+        <v>45797</v>
+      </c>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="6"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="9"/>
-      <c r="I22"/>
+      <c r="A22" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="7">
+        <v>45798</v>
+      </c>
+      <c r="C22" s="7">
+        <v>45805</v>
+      </c>
+      <c r="D22" s="8">
+        <v>132638440</v>
+      </c>
+      <c r="E22" s="14">
+        <v>3449989510</v>
+      </c>
+      <c r="F22" s="22" t="s">
+        <v>118</v>
+      </c>
+      <c r="G22" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="I22" s="21">
+        <v>45798</v>
+      </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="6"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="9"/>
-      <c r="I23"/>
+      <c r="A23" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="7">
+        <v>45797</v>
+      </c>
+      <c r="C23" s="7">
+        <v>45805</v>
+      </c>
+      <c r="D23" s="8">
+        <v>132637414</v>
+      </c>
+      <c r="E23" s="14">
+        <v>3449989059</v>
+      </c>
+      <c r="F23" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="G23" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="I23" s="21">
+        <v>45797</v>
+      </c>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="6"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="9"/>
-      <c r="I24"/>
+      <c r="A24" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="7">
+        <v>45797</v>
+      </c>
+      <c r="C24" s="7">
+        <v>45805</v>
+      </c>
+      <c r="D24" s="8">
+        <v>132641337</v>
+      </c>
+      <c r="E24" s="14">
+        <v>3449988938</v>
+      </c>
+      <c r="F24" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="G24" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="I24" s="21">
+        <v>45797</v>
+      </c>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="6"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="9"/>
-      <c r="I25"/>
+      <c r="A25" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" s="7">
+        <v>45803</v>
+      </c>
+      <c r="C25" s="7">
+        <v>45805</v>
+      </c>
+      <c r="D25" s="8">
+        <v>132697219</v>
+      </c>
+      <c r="E25" s="14">
+        <v>3449992326</v>
+      </c>
+      <c r="F25" s="22" t="s">
+        <v>122</v>
+      </c>
+      <c r="G25" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="I25" s="21">
+        <v>45803</v>
+      </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="6"/>
@@ -3331,10 +3819,9 @@
       <c r="C26" s="7"/>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
-      <c r="F26" s="9"/>
+      <c r="F26" s="15"/>
       <c r="G26" s="6"/>
       <c r="H26" s="9"/>
-      <c r="I26"/>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="6"/>
@@ -3345,7 +3832,6 @@
       <c r="F27" s="9"/>
       <c r="G27" s="6"/>
       <c r="H27" s="9"/>
-      <c r="I27"/>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="6"/>
@@ -3356,7 +3842,6 @@
       <c r="F28" s="9"/>
       <c r="G28" s="6"/>
       <c r="H28" s="9"/>
-      <c r="I28"/>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="6"/>
@@ -3367,7 +3852,6 @@
       <c r="F29" s="9"/>
       <c r="G29" s="6"/>
       <c r="H29" s="9"/>
-      <c r="I29"/>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="6"/>
@@ -3378,7 +3862,6 @@
       <c r="F30" s="9"/>
       <c r="G30" s="6"/>
       <c r="H30" s="9"/>
-      <c r="I30"/>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="6"/>
@@ -3389,7 +3872,6 @@
       <c r="F31" s="9"/>
       <c r="G31" s="6"/>
       <c r="H31" s="9"/>
-      <c r="I31"/>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="6"/>
@@ -3400,9 +3882,8 @@
       <c r="F32" s="9"/>
       <c r="G32" s="6"/>
       <c r="H32" s="9"/>
-      <c r="I32"/>
-    </row>
-    <row r="33" spans="1:9">
+    </row>
+    <row r="33" spans="1:8">
       <c r="A33" s="6"/>
       <c r="B33" s="8"/>
       <c r="C33" s="7"/>
@@ -3411,9 +3892,8 @@
       <c r="F33" s="9"/>
       <c r="G33" s="6"/>
       <c r="H33" s="9"/>
-      <c r="I33"/>
-    </row>
-    <row r="34" spans="1:9">
+    </row>
+    <row r="34" spans="1:8">
       <c r="A34" s="6"/>
       <c r="B34" s="8"/>
       <c r="C34" s="7"/>
@@ -3422,9 +3902,8 @@
       <c r="F34" s="9"/>
       <c r="G34" s="6"/>
       <c r="H34" s="9"/>
-      <c r="I34"/>
-    </row>
-    <row r="35" spans="1:9">
+    </row>
+    <row r="35" spans="1:8">
       <c r="A35" s="6"/>
       <c r="B35" s="8"/>
       <c r="C35" s="7"/>
@@ -3433,9 +3912,8 @@
       <c r="F35" s="9"/>
       <c r="G35" s="6"/>
       <c r="H35" s="9"/>
-      <c r="I35"/>
-    </row>
-    <row r="36" spans="1:9">
+    </row>
+    <row r="36" spans="1:8">
       <c r="A36" s="6"/>
       <c r="B36" s="8"/>
       <c r="C36" s="7"/>
@@ -3444,9 +3922,8 @@
       <c r="F36" s="9"/>
       <c r="G36" s="6"/>
       <c r="H36" s="9"/>
-      <c r="I36"/>
-    </row>
-    <row r="37" spans="1:9">
+    </row>
+    <row r="37" spans="1:8">
       <c r="A37" s="6"/>
       <c r="B37" s="8"/>
       <c r="C37" s="7"/>
@@ -3455,9 +3932,8 @@
       <c r="F37" s="9"/>
       <c r="G37" s="6"/>
       <c r="H37" s="9"/>
-      <c r="I37"/>
-    </row>
-    <row r="38" spans="1:9">
+    </row>
+    <row r="38" spans="1:8">
       <c r="A38" s="6"/>
       <c r="B38" s="8"/>
       <c r="C38" s="7"/>
@@ -3466,9 +3942,8 @@
       <c r="F38" s="9"/>
       <c r="G38" s="6"/>
       <c r="H38" s="9"/>
-      <c r="I38"/>
-    </row>
-    <row r="39" spans="1:9">
+    </row>
+    <row r="39" spans="1:8">
       <c r="A39" s="6"/>
       <c r="B39" s="8"/>
       <c r="C39" s="7"/>
@@ -3477,9 +3952,8 @@
       <c r="F39" s="9"/>
       <c r="G39" s="6"/>
       <c r="H39" s="9"/>
-      <c r="I39"/>
-    </row>
-    <row r="40" spans="1:9">
+    </row>
+    <row r="40" spans="1:8">
       <c r="A40" s="6"/>
       <c r="B40" s="8"/>
       <c r="C40" s="7"/>
@@ -3488,9 +3962,8 @@
       <c r="F40" s="9"/>
       <c r="G40" s="6"/>
       <c r="H40" s="9"/>
-      <c r="I40"/>
-    </row>
-    <row r="41" spans="1:9">
+    </row>
+    <row r="41" spans="1:8">
       <c r="A41" s="6"/>
       <c r="B41" s="8"/>
       <c r="C41" s="7"/>
@@ -3499,9 +3972,8 @@
       <c r="F41" s="9"/>
       <c r="G41" s="6"/>
       <c r="H41" s="9"/>
-      <c r="I41"/>
-    </row>
-    <row r="42" spans="1:9">
+    </row>
+    <row r="42" spans="1:8">
       <c r="A42" s="6"/>
       <c r="B42" s="8"/>
       <c r="C42" s="7"/>
@@ -3510,9 +3982,8 @@
       <c r="F42" s="9"/>
       <c r="G42" s="6"/>
       <c r="H42" s="9"/>
-      <c r="I42"/>
-    </row>
-    <row r="43" spans="1:9">
+    </row>
+    <row r="43" spans="1:8">
       <c r="A43" s="6"/>
       <c r="B43" s="8"/>
       <c r="C43" s="7"/>
@@ -3521,9 +3992,8 @@
       <c r="F43" s="9"/>
       <c r="G43" s="6"/>
       <c r="H43" s="9"/>
-      <c r="I43"/>
-    </row>
-    <row r="44" spans="1:9">
+    </row>
+    <row r="44" spans="1:8">
       <c r="A44" s="6"/>
       <c r="B44" s="8"/>
       <c r="C44" s="7"/>
@@ -3532,9 +4002,8 @@
       <c r="F44" s="9"/>
       <c r="G44" s="6"/>
       <c r="H44" s="9"/>
-      <c r="I44"/>
-    </row>
-    <row r="45" spans="1:9">
+    </row>
+    <row r="45" spans="1:8">
       <c r="A45" s="6"/>
       <c r="B45" s="8"/>
       <c r="C45" s="7"/>
@@ -3543,9 +4012,8 @@
       <c r="F45" s="9"/>
       <c r="G45" s="6"/>
       <c r="H45" s="9"/>
-      <c r="I45"/>
-    </row>
-    <row r="46" spans="1:9">
+    </row>
+    <row r="46" spans="1:8">
       <c r="A46" s="6"/>
       <c r="B46" s="8"/>
       <c r="C46" s="7"/>
@@ -3554,9 +4022,8 @@
       <c r="F46" s="9"/>
       <c r="G46" s="6"/>
       <c r="H46" s="9"/>
-      <c r="I46"/>
-    </row>
-    <row r="47" spans="1:9">
+    </row>
+    <row r="47" spans="1:8">
       <c r="A47" s="6"/>
       <c r="B47" s="8"/>
       <c r="C47" s="7"/>
@@ -3565,9 +4032,8 @@
       <c r="F47" s="9"/>
       <c r="G47" s="6"/>
       <c r="H47" s="9"/>
-      <c r="I47"/>
-    </row>
-    <row r="48" spans="1:9">
+    </row>
+    <row r="48" spans="1:8">
       <c r="A48" s="6"/>
       <c r="B48" s="8"/>
       <c r="C48" s="7"/>
@@ -3576,9 +4042,8 @@
       <c r="F48" s="9"/>
       <c r="G48" s="6"/>
       <c r="H48" s="9"/>
-      <c r="I48"/>
-    </row>
-    <row r="49" spans="1:9">
+    </row>
+    <row r="49" spans="1:8">
       <c r="A49" s="6"/>
       <c r="B49" s="8"/>
       <c r="C49" s="7"/>
@@ -3587,9 +4052,8 @@
       <c r="F49" s="9"/>
       <c r="G49" s="6"/>
       <c r="H49" s="9"/>
-      <c r="I49"/>
-    </row>
-    <row r="50" spans="1:9">
+    </row>
+    <row r="50" spans="1:8">
       <c r="A50" s="6"/>
       <c r="B50" s="8"/>
       <c r="C50" s="7"/>
@@ -3598,9 +4062,8 @@
       <c r="F50" s="9"/>
       <c r="G50" s="6"/>
       <c r="H50" s="9"/>
-      <c r="I50"/>
-    </row>
-    <row r="51" spans="1:9">
+    </row>
+    <row r="51" spans="1:8">
       <c r="A51" s="6"/>
       <c r="B51" s="8"/>
       <c r="C51" s="7"/>
@@ -3609,9 +4072,8 @@
       <c r="F51" s="9"/>
       <c r="G51" s="6"/>
       <c r="H51" s="9"/>
-      <c r="I51"/>
-    </row>
-    <row r="52" spans="1:9">
+    </row>
+    <row r="52" spans="1:8">
       <c r="A52" s="6"/>
       <c r="B52" s="8"/>
       <c r="C52" s="7"/>
@@ -3620,9 +4082,8 @@
       <c r="F52" s="9"/>
       <c r="G52" s="6"/>
       <c r="H52" s="9"/>
-      <c r="I52"/>
-    </row>
-    <row r="53" spans="1:9">
+    </row>
+    <row r="53" spans="1:8">
       <c r="A53" s="6"/>
       <c r="B53" s="8"/>
       <c r="C53" s="7"/>
@@ -3631,52 +4092,18 @@
       <c r="F53" s="9"/>
       <c r="G53" s="6"/>
       <c r="H53" s="9"/>
-      <c r="I53"/>
-    </row>
-    <row r="54" spans="1:9">
-      <c r="A54" s="6"/>
-      <c r="B54" s="8"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="8"/>
-      <c r="E54" s="8"/>
-      <c r="F54" s="9"/>
-      <c r="G54" s="6"/>
-      <c r="H54" s="9"/>
-      <c r="I54"/>
-    </row>
-    <row r="55" spans="1:9">
-      <c r="A55" s="6"/>
-      <c r="B55" s="8"/>
-      <c r="C55" s="7"/>
-      <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
-      <c r="F55" s="9"/>
-      <c r="G55" s="6"/>
-      <c r="H55" s="9"/>
-      <c r="I55"/>
-    </row>
-    <row r="56" spans="1:9">
-      <c r="A56" s="6"/>
-      <c r="B56" s="8"/>
-      <c r="C56" s="7"/>
-      <c r="D56" s="8"/>
-      <c r="E56" s="8"/>
-      <c r="F56" s="9"/>
-      <c r="G56" s="6"/>
-      <c r="H56" s="9"/>
-      <c r="I56"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="1">
+    <cfRule type="notContainsBlanks" priority="2">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A19" xr:uid="{4D257AA8-3FDB-42B7-A450-B3788B0ABB12}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A25" xr:uid="{4D257AA8-3FDB-42B7-A450-B3788B0ABB12}">
       <formula1>$J$2</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G42" xr:uid="{5FAA0C61-6912-46B8-8149-B719594B77CB}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G39" xr:uid="{5FAA0C61-6912-46B8-8149-B719594B77CB}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3689,7 +4116,7 @@
   <dimension ref="A1:I56"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="25.7109375" style="17" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.7109375" style="16" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="26" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="29.28515625" customWidth="1"/>
@@ -5026,7 +5453,7 @@
     <col min="6" max="6" width="36" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="20.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="42" customWidth="1"/>
-    <col min="9" max="9" width="18.7109375" style="17" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.7109375" style="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -6382,8 +6809,51 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="43" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="abf1b9912853fe4a934dbc2373304754">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d8d96f03b10d24171ef462918d18284e" ns1:_="" ns2:_="" ns3:_="">
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-469103</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-469103</Url>
+      <Description>QAFFA7D2F2TC-2102087286-469103</Description>
+    </_dlc_DocIdUrl>
+    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </DossierOwner>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ccca9d190a3c43e89f73773ee806c8b5>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ia4b831ccad64069ad2e0cbd870e9b8a>
+    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </alteradopor>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="43" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="32fbec5585ae01a22f32af5838af0c4d">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7b2552458edfdc024ce707f91c2c891f" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
     <xsd:import namespace="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea"/>
     <xsd:import namespace="ea6c6725-5210-4d6a-93cc-4cf85111ac5e"/>
@@ -6431,12 +6901,12 @@
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="http://schemas.microsoft.com/sharepoint/v3" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="_ip_UnifiedCompliancePolicyProperties" ma:index="23" nillable="true" ma:displayName="Unified Compliance Policy Properties" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyProperties">
+    <xsd:element name="_ip_UnifiedCompliancePolicyProperties" ma:index="23" nillable="true" ma:displayName="Propriedades da Política de Conformidade Unificada" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyProperties">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="_ip_UnifiedCompliancePolicyUIAction" ma:index="24" nillable="true" ma:displayName="Unified Compliance Policy UI Action" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyUIAction">
+    <xsd:element name="_ip_UnifiedCompliancePolicyUIAction" ma:index="24" nillable="true" ma:displayName="Ação de IU da Política de Conformidade Unificada" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyUIAction">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
@@ -6445,12 +6915,12 @@
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="_dlc_DocId" ma:index="8" nillable="true" ma:displayName="Document ID Value" ma:description="The value of the document ID assigned to this item." ma:indexed="true" ma:internalName="_dlc_DocId" ma:readOnly="true">
+    <xsd:element name="_dlc_DocId" ma:index="8" nillable="true" ma:displayName="Valor do ID do Documento" ma:description="O valor do ID do documento atribuído a este item." ma:indexed="true" ma:internalName="_dlc_DocId" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="_dlc_DocIdUrl" ma:index="9" nillable="true" ma:displayName="Document ID" ma:description="Permanent link to this document." ma:hidden="true" ma:internalName="_dlc_DocIdUrl" ma:readOnly="true">
+    <xsd:element name="_dlc_DocIdUrl" ma:index="9" nillable="true" ma:displayName="ID do Documento" ma:description="Ligação permanente a este documento." ma:hidden="true" ma:internalName="_dlc_DocIdUrl" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:URL">
@@ -6533,7 +7003,7 @@
         <xsd:restriction base="dms:DateTime"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Partilhado Com" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -6552,7 +7022,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Detalhes de Partilhado Com" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
@@ -6585,7 +7055,7 @@
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="26" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="10820af1-e82f-496e-bbcb-d9502914b7b2" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="26" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de Imagem" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="10820af1-e82f-496e-bbcb-d9502914b7b2" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
@@ -6663,8 +7133,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de Conteúdo"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -6753,7 +7223,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
   <Receiver>
@@ -6803,7 +7273,7 @@
 </spe:Receivers>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -6812,61 +7282,18 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-469103</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-469103</Url>
-      <Description>QAFFA7D2F2TC-2102087286-469103</Description>
-    </_dlc_DocIdUrl>
-    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </DossierOwner>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ccca9d190a3c43e89f73773ee806c8b5>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ia4b831ccad64069ad2e0cbd870e9b8a>
-    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </alteradopor>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{422E86E5-4CC6-443E-A0AA-A74CA8044393}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29EDCE3E-2594-4619-A283-B092EC3CB912}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/Arquivos/Relatório de Recusas 26.05.2025 a 01.06.2025.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/Arquivos/Relatório de Recusas 26.05.2025 a 01.06.2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms.sharepoint.com/teams/BR0010-4356589/Shared Documents/BACK-OFFICE SME/Santander/2025/Relatório de Recusas/05. Maio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{157DDAF3-AEC3-4DA9-9D77-4EABAD4D6C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{97504837-1314-4E38-8CC2-74E7E37CA753}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="4" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="26.05" sheetId="8" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="189">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -574,6 +574,77 @@
   </si>
   <si>
     <t>Chassi Irregular</t>
+  </si>
+  <si>
+    <t>MARIA DO SOCORRO DA SILVA SOUZA CARDOSO CPF 51027801234</t>
+  </si>
+  <si>
+    <t>Política de Aceitação;</t>
+  </si>
+  <si>
+    <t>Sem aceitação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AYLSON AURELIO CARDOZO                       </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, identificamos que não há po
+ssibilidade de efetuar a transferência de bônus para o(a) senhor(a
+) AYLSON AURELIO CARDOZO, pois este não consta como condutor na ap
+ólice anterior.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARLA MAGALHAES DOS SANTOS                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIANE AUXILIADORA GONCALVES DE QUEIROZ       </t>
+  </si>
+  <si>
+    <t>***FRUSTRADO***CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO - FOTO INCORRETA: pendente foto do motor, chassi, traseira lateral esquerda, traseira lateral direita</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GIZELIA NADIR DO NASCIMENTO FERREIRA         </t>
+  </si>
+  <si>
+    <t>Favor enviar cópia completa da apólice renovada na congênere ref
+erente 2025/2026 e o endosso de cancelamento dessa apólice junto a
+congênere.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LARISSA DINIZ PIQUINI                        </t>
+  </si>
+  <si>
+    <t>A pedido segurada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAVAGEM VEICULAR DO FORTE LTDA EPP           </t>
+  </si>
+  <si>
+    <t>***FRUSTRADO***CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO - FOTO INCORRETA: Foto 45º - Frente e Lateral Direita (Lateral direita não enquadrada corretamente). Hodômetro (Hodômetro Desligado (Veículo Desligado)).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LETICIA GOMES DO NASCIMENTO                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARILDA FERREIRA DA SILVA                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MICHEL SCHIPHORST                            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">OTAVIO SICHONANY DE ALMEIDA                  </t>
+  </si>
+  <si>
+    <t>Nup CANCELAMENTO 29/05/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROSELAINE DE ALMEIDA                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUBENS GUEDES                                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">WALDEMIR JESUS DOS SANTOS                    </t>
   </si>
 </sst>
 </file>
@@ -622,7 +693,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -749,12 +820,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -834,9 +916,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4352,10 +4442,10 @@
       <c r="F2" s="28" t="s">
         <v>123</v>
       </c>
-      <c r="G2" s="34" t="s">
+      <c r="G2" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="H2" s="33" t="s">
+      <c r="H2" s="23" t="s">
         <v>124</v>
       </c>
       <c r="I2" s="21">
@@ -4381,10 +4471,10 @@
       <c r="F3" s="28" t="s">
         <v>125</v>
       </c>
-      <c r="G3" s="34" t="s">
+      <c r="G3" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="H3" s="33" t="s">
+      <c r="H3" s="23" t="s">
         <v>126</v>
       </c>
       <c r="I3" s="21">
@@ -4410,7 +4500,7 @@
       <c r="F4" s="28" t="s">
         <v>127</v>
       </c>
-      <c r="G4" s="34" t="s">
+      <c r="G4" s="33" t="s">
         <v>22</v>
       </c>
       <c r="H4" s="23" t="s">
@@ -4439,7 +4529,7 @@
       <c r="F5" s="28" t="s">
         <v>129</v>
       </c>
-      <c r="G5" s="34" t="s">
+      <c r="G5" s="33" t="s">
         <v>22</v>
       </c>
       <c r="H5" s="23" t="s">
@@ -4468,7 +4558,7 @@
       <c r="F6" s="28" t="s">
         <v>130</v>
       </c>
-      <c r="G6" s="34" t="s">
+      <c r="G6" s="33" t="s">
         <v>34</v>
       </c>
       <c r="H6" s="10" t="s">
@@ -4497,7 +4587,7 @@
       <c r="F7" s="28" t="s">
         <v>131</v>
       </c>
-      <c r="G7" s="34" t="s">
+      <c r="G7" s="33" t="s">
         <v>34</v>
       </c>
       <c r="H7" s="10" t="s">
@@ -4526,7 +4616,7 @@
       <c r="F8" s="28" t="s">
         <v>133</v>
       </c>
-      <c r="G8" s="34" t="s">
+      <c r="G8" s="33" t="s">
         <v>34</v>
       </c>
       <c r="H8" s="23" t="s">
@@ -4555,7 +4645,7 @@
       <c r="F9" s="28" t="s">
         <v>135</v>
       </c>
-      <c r="G9" s="34" t="s">
+      <c r="G9" s="33" t="s">
         <v>34</v>
       </c>
       <c r="H9" s="23" t="s">
@@ -4584,7 +4674,7 @@
       <c r="F10" s="28" t="s">
         <v>137</v>
       </c>
-      <c r="G10" s="34" t="s">
+      <c r="G10" s="33" t="s">
         <v>34</v>
       </c>
       <c r="H10" s="23" t="s">
@@ -4613,10 +4703,10 @@
       <c r="F11" s="28" t="s">
         <v>139</v>
       </c>
-      <c r="G11" s="34" t="s">
+      <c r="G11" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="H11" s="33" t="s">
+      <c r="H11" s="23" t="s">
         <v>140</v>
       </c>
       <c r="I11" s="21">
@@ -4642,10 +4732,10 @@
       <c r="F12" s="28" t="s">
         <v>141</v>
       </c>
-      <c r="G12" s="34" t="s">
+      <c r="G12" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="H12" s="33" t="s">
+      <c r="H12" s="23" t="s">
         <v>142</v>
       </c>
       <c r="I12" s="21">
@@ -4671,7 +4761,7 @@
       <c r="F13" s="28" t="s">
         <v>143</v>
       </c>
-      <c r="G13" s="34" t="s">
+      <c r="G13" s="33" t="s">
         <v>34</v>
       </c>
       <c r="H13" s="23" t="s">
@@ -4700,7 +4790,7 @@
       <c r="F14" s="28" t="s">
         <v>145</v>
       </c>
-      <c r="G14" s="34" t="s">
+      <c r="G14" s="33" t="s">
         <v>34</v>
       </c>
       <c r="H14" s="23" t="s">
@@ -4729,7 +4819,7 @@
       <c r="F15" s="28" t="s">
         <v>147</v>
       </c>
-      <c r="G15" s="34" t="s">
+      <c r="G15" s="33" t="s">
         <v>22</v>
       </c>
       <c r="H15" s="23" t="s">
@@ -4758,7 +4848,7 @@
       <c r="F16" s="28" t="s">
         <v>149</v>
       </c>
-      <c r="G16" s="34" t="s">
+      <c r="G16" s="33" t="s">
         <v>34</v>
       </c>
       <c r="H16" s="23" t="s">
@@ -4787,10 +4877,10 @@
       <c r="F17" s="28" t="s">
         <v>151</v>
       </c>
-      <c r="G17" s="34" t="s">
+      <c r="G17" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="H17" s="33" t="s">
+      <c r="H17" s="23" t="s">
         <v>152</v>
       </c>
       <c r="I17" s="21">
@@ -4816,7 +4906,7 @@
       <c r="F18" s="28" t="s">
         <v>153</v>
       </c>
-      <c r="G18" s="34" t="s">
+      <c r="G18" s="33" t="s">
         <v>22</v>
       </c>
       <c r="H18" s="23" t="s">
@@ -4845,7 +4935,7 @@
       <c r="F19" s="28" t="s">
         <v>154</v>
       </c>
-      <c r="G19" s="34" t="s">
+      <c r="G19" s="33" t="s">
         <v>53</v>
       </c>
       <c r="H19" s="23" t="s">
@@ -4874,7 +4964,7 @@
       <c r="F20" s="28" t="s">
         <v>155</v>
       </c>
-      <c r="G20" s="34" t="s">
+      <c r="G20" s="33" t="s">
         <v>53</v>
       </c>
       <c r="H20" s="23" t="s">
@@ -4903,7 +4993,7 @@
       <c r="F21" s="28" t="s">
         <v>156</v>
       </c>
-      <c r="G21" s="34" t="s">
+      <c r="G21" s="33" t="s">
         <v>34</v>
       </c>
       <c r="H21" s="23" t="s">
@@ -4932,7 +5022,7 @@
       <c r="F22" s="28" t="s">
         <v>157</v>
       </c>
-      <c r="G22" s="34" t="s">
+      <c r="G22" s="33" t="s">
         <v>30</v>
       </c>
       <c r="H22" s="23" t="s">
@@ -4961,7 +5051,7 @@
       <c r="F23" s="28" t="s">
         <v>158</v>
       </c>
-      <c r="G23" s="34" t="s">
+      <c r="G23" s="33" t="s">
         <v>53</v>
       </c>
       <c r="H23" s="23" t="s">
@@ -4990,7 +5080,7 @@
       <c r="F24" s="28" t="s">
         <v>159</v>
       </c>
-      <c r="G24" s="34" t="s">
+      <c r="G24" s="33" t="s">
         <v>53</v>
       </c>
       <c r="H24" s="23" t="s">
@@ -5019,7 +5109,7 @@
       <c r="F25" s="28" t="s">
         <v>160</v>
       </c>
-      <c r="G25" s="34" t="s">
+      <c r="G25" s="33" t="s">
         <v>53</v>
       </c>
       <c r="H25" s="23" t="s">
@@ -5048,7 +5138,7 @@
       <c r="F26" s="28" t="s">
         <v>161</v>
       </c>
-      <c r="G26" s="34" t="s">
+      <c r="G26" s="33" t="s">
         <v>53</v>
       </c>
       <c r="H26" s="23" t="s">
@@ -5077,7 +5167,7 @@
       <c r="F27" s="28" t="s">
         <v>162</v>
       </c>
-      <c r="G27" s="34" t="s">
+      <c r="G27" s="33" t="s">
         <v>30</v>
       </c>
       <c r="H27" s="23" t="s">
@@ -5387,18 +5477,18 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BF216D7-F2B3-4C54-A7B9-7048B06C2C75}">
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5703125" customWidth="1"/>
     <col min="3" max="3" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.28515625" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
     <col min="6" max="6" width="31.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="20.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="28.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.7109375" style="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -5446,7 +5536,7 @@
       <c r="E2" s="14">
         <v>3449995351</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="28" t="s">
         <v>165</v>
       </c>
       <c r="G2" s="6" t="s">
@@ -5460,200 +5550,418 @@
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="9"/>
+      <c r="B3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="D3" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="8">
+        <v>3449991237</v>
+      </c>
+      <c r="F3" s="36" t="s">
+        <v>167</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="11"/>
+      <c r="B4" s="7">
+        <v>45805</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="D4" s="26">
+        <v>132733612</v>
+      </c>
+      <c r="E4" s="34">
+        <v>3449993976</v>
+      </c>
+      <c r="F4" s="28" t="s">
+        <v>170</v>
+      </c>
+      <c r="G4" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="I4" s="21">
+        <v>45807</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="11"/>
+      <c r="B5" s="7">
+        <v>45799</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="D5" s="26">
+        <v>132665093</v>
+      </c>
+      <c r="E5" s="34">
+        <v>3449991116</v>
+      </c>
+      <c r="F5" s="28" t="s">
+        <v>172</v>
+      </c>
+      <c r="G5" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="I5" s="21">
+        <v>45799</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="11"/>
+      <c r="B6" s="7">
+        <v>45800</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="D6" s="26">
+        <v>132685840</v>
+      </c>
+      <c r="E6" s="34">
+        <v>3449991963</v>
+      </c>
+      <c r="F6" s="28" t="s">
+        <v>173</v>
+      </c>
+      <c r="G6" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="I6" s="21">
+        <v>45800</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="11"/>
+      <c r="B7" s="7">
+        <v>45807</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="D7" s="26">
+        <v>132603575</v>
+      </c>
+      <c r="E7" s="34">
+        <v>3449987893</v>
+      </c>
+      <c r="F7" s="28" t="s">
+        <v>175</v>
+      </c>
+      <c r="G7" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="I7" s="21">
+        <v>45798</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="11"/>
+      <c r="B8" s="7">
+        <v>45804</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="D8" s="26">
+        <v>132703990</v>
+      </c>
+      <c r="E8" s="34">
+        <v>3449992645</v>
+      </c>
+      <c r="F8" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="G8" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="I8" s="21">
+        <v>45807</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="11"/>
+      <c r="B9" s="7">
+        <v>45800</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="D9" s="26">
+        <v>132687055</v>
+      </c>
+      <c r="E9" s="34">
+        <v>3449992007</v>
+      </c>
+      <c r="F9" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="G9" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="I9" s="21">
+        <v>45800</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="11"/>
+      <c r="B10" s="7">
+        <v>45799</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="D10" s="26">
+        <v>132659107</v>
+      </c>
+      <c r="E10" s="34">
+        <v>3449990731</v>
+      </c>
+      <c r="F10" s="28" t="s">
+        <v>181</v>
+      </c>
+      <c r="G10" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="I10" s="21">
+        <v>45799</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="11"/>
+      <c r="B11" s="7">
+        <v>45803</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="D11" s="26">
+        <v>132699038</v>
+      </c>
+      <c r="E11" s="34">
+        <v>3449992392</v>
+      </c>
+      <c r="F11" s="28" t="s">
+        <v>182</v>
+      </c>
+      <c r="G11" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11" s="21">
+        <v>45803</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="11"/>
+      <c r="B12" s="7">
+        <v>45799</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="D12" s="26">
+        <v>132662090</v>
+      </c>
+      <c r="E12" s="34">
+        <v>3449990885</v>
+      </c>
+      <c r="F12" s="28" t="s">
+        <v>183</v>
+      </c>
+      <c r="G12" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="I12" s="21">
+        <v>45799</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="11"/>
+      <c r="B13" s="7">
+        <v>45805</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="D13" s="26">
+        <v>132734254</v>
+      </c>
+      <c r="E13" s="34">
+        <v>3449994010</v>
+      </c>
+      <c r="F13" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="G13" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="I13" s="21">
+        <v>45806</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="11"/>
+      <c r="B14" s="7">
+        <v>45820</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="D14" s="26">
+        <v>132717894</v>
+      </c>
+      <c r="E14" s="34">
+        <v>3449993173</v>
+      </c>
+      <c r="F14" s="28" t="s">
+        <v>186</v>
+      </c>
+      <c r="G14" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="I14" s="21">
+        <v>45806</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="11"/>
+      <c r="B15" s="7">
+        <v>45799</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="D15" s="26">
+        <v>132676717</v>
+      </c>
+      <c r="E15" s="34">
+        <v>3449990555</v>
+      </c>
+      <c r="F15" s="28" t="s">
+        <v>187</v>
+      </c>
+      <c r="G15" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="I15" s="21">
+        <v>45799</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="11"/>
+      <c r="B16" s="7">
+        <v>45803</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="D16" s="26">
+        <v>132694770</v>
+      </c>
+      <c r="E16" s="34">
+        <v>3449992216</v>
+      </c>
+      <c r="F16" s="28" t="s">
+        <v>188</v>
+      </c>
+      <c r="G16" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="I16" s="21">
+        <v>45806</v>
+      </c>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="A17" s="6"/>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
-      <c r="D17" s="8"/>
+      <c r="D17" s="24"/>
       <c r="E17" s="14"/>
-      <c r="F17" s="12"/>
+      <c r="F17" s="19"/>
       <c r="G17" s="6"/>
       <c r="H17" s="9"/>
-      <c r="I17" s="11"/>
+      <c r="I17" s="21"/>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="A18" s="6"/>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
       <c r="D18" s="8"/>
@@ -5661,28 +5969,25 @@
       <c r="F18" s="12"/>
       <c r="G18" s="6"/>
       <c r="H18" s="9"/>
-      <c r="I18" s="11"/>
+      <c r="I18" s="21"/>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B19" s="7"/>
+      <c r="A19" s="6"/>
+      <c r="B19" s="8"/>
       <c r="C19" s="7"/>
       <c r="D19" s="8"/>
       <c r="E19" s="14"/>
-      <c r="F19" s="12"/>
+      <c r="F19" s="13"/>
       <c r="G19" s="6"/>
       <c r="H19" s="9"/>
-      <c r="I19" s="11"/>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="6"/>
       <c r="B20" s="8"/>
       <c r="C20" s="7"/>
       <c r="D20" s="8"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="13"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="15"/>
       <c r="G20" s="6"/>
       <c r="H20" s="9"/>
     </row>
@@ -5692,7 +5997,7 @@
       <c r="C21" s="7"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
-      <c r="F21" s="15"/>
+      <c r="F21" s="9"/>
       <c r="G21" s="6"/>
       <c r="H21" s="9"/>
     </row>
@@ -6036,27 +6341,17 @@
       <c r="G55" s="6"/>
       <c r="H55" s="9"/>
     </row>
-    <row r="56" spans="1:8">
-      <c r="A56" s="6"/>
-      <c r="B56" s="8"/>
-      <c r="C56" s="7"/>
-      <c r="D56" s="8"/>
-      <c r="E56" s="8"/>
-      <c r="F56" s="9"/>
-      <c r="G56" s="6"/>
-      <c r="H56" s="9"/>
-    </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="2">
+    <cfRule type="notContainsBlanks" priority="3">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A19" xr:uid="{69840FBE-03D6-48CB-B553-2E7186E1B4BD}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A18" xr:uid="{69840FBE-03D6-48CB-B553-2E7186E1B4BD}">
       <formula1>$J$2</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G42" xr:uid="{AF5C7196-9DAE-4339-82D4-9412023E2B2A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G41" xr:uid="{AF5C7196-9DAE-4339-82D4-9412023E2B2A}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7433,8 +7728,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="43" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="32fbec5585ae01a22f32af5838af0c4d">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7b2552458edfdc024ce707f91c2c891f" ns1:_="" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="43" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="abf1b9912853fe4a934dbc2373304754">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d8d96f03b10d24171ef462918d18284e" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
     <xsd:import namespace="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea"/>
     <xsd:import namespace="ea6c6725-5210-4d6a-93cc-4cf85111ac5e"/>
@@ -7482,12 +7777,12 @@
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="http://schemas.microsoft.com/sharepoint/v3" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="_ip_UnifiedCompliancePolicyProperties" ma:index="23" nillable="true" ma:displayName="Propriedades da Política de Conformidade Unificada" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyProperties">
+    <xsd:element name="_ip_UnifiedCompliancePolicyProperties" ma:index="23" nillable="true" ma:displayName="Unified Compliance Policy Properties" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyProperties">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="_ip_UnifiedCompliancePolicyUIAction" ma:index="24" nillable="true" ma:displayName="Ação de IU da Política de Conformidade Unificada" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyUIAction">
+    <xsd:element name="_ip_UnifiedCompliancePolicyUIAction" ma:index="24" nillable="true" ma:displayName="Unified Compliance Policy UI Action" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyUIAction">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
@@ -7496,12 +7791,12 @@
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="_dlc_DocId" ma:index="8" nillable="true" ma:displayName="Valor do ID do Documento" ma:description="O valor do ID do documento atribuído a este item." ma:indexed="true" ma:internalName="_dlc_DocId" ma:readOnly="true">
+    <xsd:element name="_dlc_DocId" ma:index="8" nillable="true" ma:displayName="Document ID Value" ma:description="The value of the document ID assigned to this item." ma:indexed="true" ma:internalName="_dlc_DocId" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="_dlc_DocIdUrl" ma:index="9" nillable="true" ma:displayName="ID do Documento" ma:description="Ligação permanente a este documento." ma:hidden="true" ma:internalName="_dlc_DocIdUrl" ma:readOnly="true">
+    <xsd:element name="_dlc_DocIdUrl" ma:index="9" nillable="true" ma:displayName="Document ID" ma:description="Permanent link to this document." ma:hidden="true" ma:internalName="_dlc_DocIdUrl" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:URL">
@@ -7584,7 +7879,7 @@
         <xsd:restriction base="dms:DateTime"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Partilhado Com" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -7603,7 +7898,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Detalhes de Partilhado Com" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
@@ -7636,7 +7931,7 @@
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="26" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de Imagem" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="10820af1-e82f-496e-bbcb-d9502914b7b2" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="26" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="10820af1-e82f-496e-bbcb-d9502914b7b2" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
@@ -7714,8 +8009,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de Conteúdo"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -7805,58 +8100,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-469103</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-469103</Url>
-      <Description>QAFFA7D2F2TC-2102087286-469103</Description>
-    </_dlc_DocIdUrl>
-    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </DossierOwner>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ccca9d190a3c43e89f73773ee806c8b5>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ia4b831ccad64069ad2e0cbd870e9b8a>
-    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </alteradopor>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
   <Receiver>
@@ -7906,12 +8149,64 @@
 </spe:Receivers>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-469103</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-469103</Url>
+      <Description>QAFFA7D2F2TC-2102087286-469103</Description>
+    </_dlc_DocIdUrl>
+    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </DossierOwner>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ccca9d190a3c43e89f73773ee806c8b5>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ia4b831ccad64069ad2e0cbd870e9b8a>
+    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </alteradopor>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65843FDC-03DE-41BE-82A4-747E1DE7FEDB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91B337B1-98AE-437B-BA65-10339981CDFC}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7919,5 +8214,5 @@
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
 </file>